--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.2637362637362637</v>
+        <v>0.1566265060240964</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.2676056338028169</v>
+        <v>0.2714285714285714</v>
       </c>
       <c r="D2">
-        <v>0.8125</v>
+        <v>0.8869565217391304</v>
       </c>
       <c r="E2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.1566265060240964</v>
+        <v>0.1341463414634146</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.2714285714285714</v>
+        <v>0.2681159420289855</v>
       </c>
       <c r="D2">
-        <v>0.8869565217391304</v>
+        <v>0.9017857142857143</v>
       </c>
       <c r="E2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
